--- a/excel/output_stats_sfvv/gemver/EfficiencyStats.xlsx
+++ b/excel/output_stats_sfvv/gemver/EfficiencyStats.xlsx
@@ -499,16 +499,16 @@
         <v>41.1417</v>
       </c>
       <c r="F2" t="n">
-        <v>353.5</v>
+        <v>355.68</v>
       </c>
       <c r="G2" t="n">
-        <v>355.79</v>
+        <v>358.51</v>
       </c>
       <c r="H2" t="n">
-        <v>351.229</v>
+        <v>352.041</v>
       </c>
       <c r="I2" t="n">
-        <v>351.432</v>
+        <v>352.392</v>
       </c>
       <c r="J2" t="n">
         <v>226227000</v>
